--- a/Data/HSC2024.xlsx
+++ b/Data/HSC2024.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Business\Result analysis\HSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Business\Result analysis\HSC_Purandar_Analysis\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552F6883-EB72-4CDB-8323-16D43A955742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
